--- a/ig/DM-MARS-2026/CodeSystem-TRE-R66-CategorieEtablissement.xlsx
+++ b/ig/DM-MARS-2026/CodeSystem-TRE-R66-CategorieEtablissement.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260223120000</t>
+    <t>20260330120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T12:00:00+01:00</t>
+    <t>2026-03-30T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-MARS-2026/CodeSystem-TRE-R66-CategorieEtablissement.xlsx
+++ b/ig/DM-MARS-2026/CodeSystem-TRE-R66-CategorieEtablissement.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1039" uniqueCount="709">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1043" uniqueCount="711">
   <si>
     <t>Property</t>
   </si>
@@ -118,1068 +118,1068 @@
     <t>Count</t>
   </si>
   <si>
+    <t>322</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Uri</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>dateValid</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateValid</t>
+  </si>
+  <si>
+    <t>Date de validité d'un code concept</t>
+  </si>
+  <si>
+    <t>dateTime</t>
+  </si>
+  <si>
+    <t>dateMaj</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateMaj</t>
+  </si>
+  <si>
+    <t>Date de mise à jour d'un code concept</t>
+  </si>
+  <si>
+    <t>dateFin</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateFin</t>
+  </si>
+  <si>
+    <t>Date de fin d'exploitation d'un code concept</t>
+  </si>
+  <si>
+    <t>deprecationDate</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/concept-properties#deprecationDate</t>
+  </si>
+  <si>
+    <t>Date Concept was deprecated</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/concept-properties#status</t>
+  </si>
+  <si>
+    <t>A property that indicates the status of the concept.</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>retirementDate</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/concept-properties#retirementDate</t>
+  </si>
+  <si>
+    <t>Date Concept was retired</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>Display</t>
+  </si>
+  <si>
+    <t>Definition</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>001</t>
+  </si>
+  <si>
+    <t>Autres lits de m.R.</t>
+  </si>
+  <si>
+    <t>002</t>
+  </si>
+  <si>
+    <t>Autres places de l-f.</t>
+  </si>
+  <si>
+    <t>003</t>
+  </si>
+  <si>
+    <t>Autres lits de l-s</t>
+  </si>
+  <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>Centre Hospitalier Régional (C.H.R.)</t>
+  </si>
+  <si>
+    <t>106</t>
+  </si>
+  <si>
+    <t>Centre hospitalier, ex Hôpital local</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>Etablissement de Convalescence et de Repos</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>Etablissement de santé privé autorisé en SSR</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>Centre de Convalescence Cure ou Réadaptation</t>
+  </si>
+  <si>
+    <t>114</t>
+  </si>
+  <si>
+    <t>Hôpital des armées</t>
+  </si>
+  <si>
+    <t>115</t>
+  </si>
+  <si>
+    <t>Etablissement de Soins du Service de Santé des Armées</t>
+  </si>
+  <si>
+    <t>119</t>
+  </si>
+  <si>
+    <t>Maison de Régime</t>
+  </si>
+  <si>
+    <t>122</t>
+  </si>
+  <si>
+    <t>Etablissement Soins Obstétriques Chirurgico-Gynécologiques</t>
+  </si>
+  <si>
+    <t>124</t>
+  </si>
+  <si>
+    <t>Centre de Santé</t>
+  </si>
+  <si>
+    <t>125</t>
+  </si>
+  <si>
+    <t>Centre de Santé Dentaire</t>
+  </si>
+  <si>
+    <t>126</t>
+  </si>
+  <si>
+    <t>Etablissement Thermal</t>
+  </si>
+  <si>
+    <t>127</t>
+  </si>
+  <si>
+    <t>Hospitalisation à Domicile</t>
+  </si>
+  <si>
+    <t>128</t>
+  </si>
+  <si>
+    <t>Etablissement de Soins Chirurgicaux</t>
+  </si>
+  <si>
+    <t>129</t>
+  </si>
+  <si>
+    <t>Etablissement de Soins Médicaux</t>
+  </si>
+  <si>
+    <t>130</t>
+  </si>
+  <si>
+    <t>Centre de Soins Médicaux</t>
+  </si>
+  <si>
+    <t>131</t>
+  </si>
+  <si>
+    <t>Centre de Lutte Contre Cancer</t>
+  </si>
+  <si>
+    <t>132</t>
+  </si>
+  <si>
+    <t>Etablissement de Transfusion Sanguine</t>
+  </si>
+  <si>
+    <t>135</t>
+  </si>
+  <si>
+    <t>Etablissement Réadaptation Fonctionnelle</t>
+  </si>
+  <si>
+    <t>136</t>
+  </si>
+  <si>
+    <t>Banque de Sperme</t>
+  </si>
+  <si>
+    <t>137</t>
+  </si>
+  <si>
+    <t>Banque d'Organes</t>
+  </si>
+  <si>
+    <t>138</t>
+  </si>
+  <si>
+    <t>Centre de Dialyse Périodique</t>
+  </si>
+  <si>
+    <t>139</t>
+  </si>
+  <si>
+    <t>Centre de Dialyse et d'entraînement à la Dialyse</t>
+  </si>
+  <si>
+    <t>140</t>
+  </si>
+  <si>
+    <t>Centre d'Entraînement à la Dialyse</t>
+  </si>
+  <si>
+    <t>141</t>
+  </si>
+  <si>
+    <t>Centre de dialyse</t>
+  </si>
+  <si>
+    <t>142</t>
+  </si>
+  <si>
+    <t>Dispensaire Antituberculeux</t>
+  </si>
+  <si>
+    <t>143</t>
+  </si>
+  <si>
+    <t>Centre de Vaccination BCG</t>
+  </si>
+  <si>
+    <t>144</t>
+  </si>
+  <si>
+    <t>Etablissement de Lutte Contre la Tuberculose</t>
+  </si>
+  <si>
+    <t>146</t>
+  </si>
+  <si>
+    <t>Structure d'Alternative à la dialyse en centre</t>
+  </si>
+  <si>
+    <t>156</t>
+  </si>
+  <si>
+    <t>Centre Médico-Psychologique (C.M.P.)</t>
+  </si>
+  <si>
+    <t>157</t>
+  </si>
+  <si>
+    <t>Centre de Postcure</t>
+  </si>
+  <si>
+    <t>159</t>
+  </si>
+  <si>
+    <t>Centre Parental</t>
+  </si>
+  <si>
+    <t>160</t>
+  </si>
+  <si>
+    <t>Centre de Soins Spécifiques pour Toxicomanes (C.S.S.T.)</t>
+  </si>
+  <si>
+    <t>161</t>
+  </si>
+  <si>
+    <t>Maison de Santé pour Maladies Mentales</t>
+  </si>
+  <si>
+    <t>162</t>
+  </si>
+  <si>
+    <t>Centre de Cure Ambulatoire en Alcoologie (C.C.A.A.)</t>
+  </si>
+  <si>
+    <t>163</t>
+  </si>
+  <si>
+    <t>Maison d'Enfants à Caractère Sanitaire Temporaire</t>
+  </si>
+  <si>
+    <t>164</t>
+  </si>
+  <si>
+    <t>Etablissements Expérimentaux Accueil de la Petite Enfance</t>
+  </si>
+  <si>
+    <t>165</t>
+  </si>
+  <si>
+    <t>Appartement de Coordination Thérapeutique (A.C.T.)</t>
+  </si>
+  <si>
+    <t>166</t>
+  </si>
+  <si>
+    <t>Centre Parents-Enfants de moins de 3 ans</t>
+  </si>
+  <si>
+    <t>167</t>
+  </si>
+  <si>
+    <t>Crèche Collective</t>
+  </si>
+  <si>
+    <t>168</t>
+  </si>
+  <si>
+    <t>Service Accueil Familial pour la Petite Enfance</t>
+  </si>
+  <si>
+    <t>169</t>
+  </si>
+  <si>
+    <t>Crèche Multi Accueil Collectif et Familial</t>
+  </si>
+  <si>
+    <t>170</t>
+  </si>
+  <si>
+    <t>Halte Garderie</t>
+  </si>
+  <si>
+    <t>171</t>
+  </si>
+  <si>
+    <t>Garderie et Jardin d'Enfants</t>
+  </si>
+  <si>
+    <t>172</t>
+  </si>
+  <si>
+    <t>Pouponnière à Caractère Social</t>
+  </si>
+  <si>
+    <t>173</t>
+  </si>
+  <si>
+    <t>Pouponnière à Caractère Sanitaire</t>
+  </si>
+  <si>
+    <t>174</t>
+  </si>
+  <si>
+    <t>Etablissement d'Accueil Collectif Régulier et Occasionnel</t>
+  </si>
+  <si>
+    <t>175</t>
+  </si>
+  <si>
+    <t>Foyer de l'Enfance</t>
+  </si>
+  <si>
+    <t>176</t>
+  </si>
+  <si>
+    <t>Village d'Enfants</t>
+  </si>
+  <si>
+    <t>177</t>
+  </si>
+  <si>
+    <t>Maison d'Enfants à Caractère Social</t>
+  </si>
+  <si>
+    <t>178</t>
+  </si>
+  <si>
+    <t>Ctre.Accueil- Accomp.Réduc.Risq.Usag. Drogues (C.A.A.R.U.D.)</t>
+  </si>
+  <si>
+    <t>179</t>
+  </si>
+  <si>
+    <t>Maison d'Enfants à Caractère Sanitaire Permanente</t>
+  </si>
+  <si>
+    <t>180</t>
+  </si>
+  <si>
+    <t>Lits Halte Soins Santé (L.H.S.S.)</t>
+  </si>
+  <si>
+    <t>181</t>
+  </si>
+  <si>
+    <t>Maison Familiale de Vacances</t>
+  </si>
+  <si>
+    <t>182</t>
+  </si>
+  <si>
+    <t>Service d'Éducation Spéciale et de Soins à Domicile</t>
+  </si>
+  <si>
+    <t>183</t>
+  </si>
+  <si>
+    <t>Institut Médico-Educatif (I.M.E.)</t>
+  </si>
+  <si>
+    <t>184</t>
+  </si>
+  <si>
+    <t>Institut Médico-Pédagogique (I.M.P.)</t>
+  </si>
+  <si>
+    <t>185</t>
+  </si>
+  <si>
+    <t>Institut Médico-Professionnel (I.M.Pro.)</t>
+  </si>
+  <si>
+    <t>186</t>
+  </si>
+  <si>
+    <t>Institut Thérapeutique Éducatif et Pédagogique (I.T.E.P.)</t>
+  </si>
+  <si>
+    <t>188</t>
+  </si>
+  <si>
+    <t>Etablissement pour Enfants ou Adolescents Polyhandicapés</t>
+  </si>
+  <si>
+    <t>189</t>
+  </si>
+  <si>
+    <t>Centre Médico-Psycho-Pédagogique (C.M.P.P.)</t>
+  </si>
+  <si>
+    <t>190</t>
+  </si>
+  <si>
+    <t>Centre Action Médico-Sociale Précoce (C.A.M.S.P.)</t>
+  </si>
+  <si>
+    <t>191</t>
+  </si>
+  <si>
+    <t>Etablissement pour Déficients Moteurs Cérébraux</t>
+  </si>
+  <si>
+    <t>192</t>
+  </si>
+  <si>
+    <t>Institut d'éducation motrice</t>
+  </si>
+  <si>
+    <t>193</t>
+  </si>
+  <si>
+    <t>Etablissement pour Déficients Moteurs et Moteurs Cérébraux</t>
+  </si>
+  <si>
+    <t>194</t>
+  </si>
+  <si>
+    <t>Institut pour Déficients Visuels</t>
+  </si>
+  <si>
+    <t>195</t>
+  </si>
+  <si>
+    <t>Institut pour Déficients Auditifs</t>
+  </si>
+  <si>
+    <t>196</t>
+  </si>
+  <si>
+    <t>Institut d'Education Sensorielle Sourd-Aveugle</t>
+  </si>
+  <si>
+    <t>197</t>
+  </si>
+  <si>
+    <t>Centre soins accompagnement prévention addictologie (CSAPA)</t>
+  </si>
+  <si>
+    <t>198</t>
+  </si>
+  <si>
+    <t>Établissement et Service de Préorientation</t>
+  </si>
+  <si>
+    <t>199</t>
+  </si>
+  <si>
+    <t>Hospice</t>
+  </si>
+  <si>
+    <t>200</t>
+  </si>
+  <si>
+    <t>Maison de Retraite</t>
+  </si>
+  <si>
+    <t>202</t>
+  </si>
+  <si>
+    <t>Résidences autonomie</t>
+  </si>
+  <si>
+    <t>205</t>
+  </si>
+  <si>
+    <t>Foyer Club Restaurant</t>
+  </si>
+  <si>
+    <t>207</t>
+  </si>
+  <si>
+    <t>Centre de Jour pour Personnes Agées</t>
+  </si>
+  <si>
+    <t>208</t>
+  </si>
+  <si>
+    <t>Service d'Aide Ménagère à Domicile</t>
+  </si>
+  <si>
+    <t>209</t>
+  </si>
+  <si>
+    <t>Service autonomie aide et soins (SAAS)</t>
+  </si>
+  <si>
+    <t>212</t>
+  </si>
+  <si>
+    <t>Alarme Médico-Sociale</t>
+  </si>
+  <si>
+    <t>213</t>
+  </si>
+  <si>
+    <t>Lits d'Accueil Médicalisés (L.A.M.)</t>
+  </si>
+  <si>
+    <t>214</t>
+  </si>
+  <si>
+    <t>Centre Hébergement &amp; Réinsertion Sociale (C.H.R.S.)</t>
+  </si>
+  <si>
+    <t>215</t>
+  </si>
+  <si>
+    <t>Maison Relai</t>
+  </si>
+  <si>
+    <t>216</t>
+  </si>
+  <si>
+    <t>Résidence Hôtelière à Vocation Sociale (R.H.V.S)</t>
+  </si>
+  <si>
+    <t>217</t>
+  </si>
+  <si>
+    <t>Cité de Transit</t>
+  </si>
+  <si>
+    <t>218</t>
+  </si>
+  <si>
+    <t>Aire Station Nomades</t>
+  </si>
+  <si>
+    <t>219</t>
+  </si>
+  <si>
+    <t>Autre Centre d'Accueil</t>
+  </si>
+  <si>
+    <t>220</t>
+  </si>
+  <si>
+    <t>Centre Social</t>
+  </si>
+  <si>
+    <t>221</t>
+  </si>
+  <si>
+    <t>Bureau d'Aide Psychologique Universitaire (B.A.P.U.)</t>
+  </si>
+  <si>
+    <t>223</t>
+  </si>
+  <si>
+    <t>Protection Maternelle et Infantile (P.M.I.)</t>
+  </si>
+  <si>
+    <t>224</t>
+  </si>
+  <si>
+    <t>Etablissement de Consultation Pré et Post-natale</t>
+  </si>
+  <si>
+    <t>225</t>
+  </si>
+  <si>
+    <t>Consultations de Nourrissons</t>
+  </si>
+  <si>
+    <t>228</t>
+  </si>
+  <si>
+    <t>Centre de Santé Sexuelle</t>
+  </si>
+  <si>
+    <t>229</t>
+  </si>
+  <si>
+    <t>Consultation Problèmes naissance</t>
+  </si>
+  <si>
+    <t>230</t>
+  </si>
+  <si>
+    <t>Etablissement Consultation Protection Infantile</t>
+  </si>
+  <si>
+    <t>231</t>
+  </si>
+  <si>
+    <t>Espaces de vie affective, relationnelle et sexuelle (EVARS)</t>
+  </si>
+  <si>
+    <t>233</t>
+  </si>
+  <si>
+    <t>Lactarium</t>
+  </si>
+  <si>
+    <t>236</t>
+  </si>
+  <si>
+    <t>Centre Placement Familial Socio-Educatif (C.P.F.S.E.)</t>
+  </si>
+  <si>
+    <t>237</t>
+  </si>
+  <si>
+    <t>Centre de Placement Familial Spécialisé</t>
+  </si>
+  <si>
+    <t>238</t>
+  </si>
+  <si>
+    <t>Centre d'Accueil Familial Spécialisé</t>
+  </si>
+  <si>
+    <t>241</t>
+  </si>
+  <si>
+    <t>Établissement de Placement</t>
+  </si>
+  <si>
+    <t>242</t>
+  </si>
+  <si>
+    <t>Service d’Activité de Jour</t>
+  </si>
+  <si>
+    <t>246</t>
+  </si>
+  <si>
+    <t>Etablissement et Service d'Aide par le Travail (E.S.A.T.)</t>
+  </si>
+  <si>
+    <t>247</t>
+  </si>
+  <si>
+    <t>Entreprise adaptée</t>
+  </si>
+  <si>
+    <t>249</t>
+  </si>
+  <si>
+    <t>Établissement et Service de Réadaptation Professionnelle</t>
+  </si>
+  <si>
+    <t>250</t>
+  </si>
+  <si>
+    <t>Centre Réentrainement au travail</t>
+  </si>
+  <si>
+    <t>251</t>
+  </si>
+  <si>
+    <t>Maison Vacances pour Handicapés</t>
+  </si>
+  <si>
+    <t>252</t>
+  </si>
+  <si>
+    <t>Foyer Hébergement Adultes Handicapés</t>
+  </si>
+  <si>
+    <t>253</t>
+  </si>
+  <si>
+    <t>Foyer d'Accueil Polyvalent pour Adultes Handicapés</t>
+  </si>
+  <si>
+    <t>255</t>
+  </si>
+  <si>
+    <t>Maison d'Accueil Spécialisée (M.A.S.)</t>
+  </si>
+  <si>
+    <t>256</t>
+  </si>
+  <si>
+    <t>Foyer Travailleurs Migrants non transformé en Résidence Soc.</t>
+  </si>
+  <si>
+    <t>257</t>
+  </si>
+  <si>
+    <t>Foyers de jeunes travailleurs</t>
+  </si>
+  <si>
+    <t>258</t>
+  </si>
+  <si>
+    <t>Maisons Relais - Pensions de Famille</t>
+  </si>
+  <si>
+    <t>259</t>
+  </si>
+  <si>
+    <t>Autres résidences sociales</t>
+  </si>
+  <si>
+    <t>261</t>
+  </si>
+  <si>
+    <t>D.D.A.S.S.</t>
+  </si>
+  <si>
+    <t>262</t>
+  </si>
+  <si>
+    <t>Etablissement Régional d'Enseignement Adapté</t>
+  </si>
+  <si>
+    <t>265</t>
+  </si>
+  <si>
+    <t>Section Education Spéciale Classe Atelier</t>
+  </si>
+  <si>
+    <t>266</t>
+  </si>
+  <si>
+    <t>Dispensaire Antivénérien</t>
+  </si>
+  <si>
+    <t>267</t>
+  </si>
+  <si>
+    <t>Dispensaire Antihansénien</t>
+  </si>
+  <si>
+    <t>268</t>
+  </si>
+  <si>
+    <t>Centre Médico-Scolaire</t>
+  </si>
+  <si>
+    <t>269</t>
+  </si>
+  <si>
+    <t>Centre de Médecine Universitaire</t>
+  </si>
+  <si>
+    <t>270</t>
+  </si>
+  <si>
+    <t>Centre de Médecine Sportive</t>
+  </si>
+  <si>
+    <t>271</t>
+  </si>
+  <si>
+    <t>Maison d'accueil Hospitalière</t>
+  </si>
+  <si>
+    <t>272</t>
+  </si>
+  <si>
+    <t>Ecole d'ambulanciers</t>
+  </si>
+  <si>
+    <t>273</t>
+  </si>
+  <si>
+    <t>Institut de formation en soins infirmiers (I.F.S.I.)</t>
+  </si>
+  <si>
+    <t>274</t>
+  </si>
+  <si>
+    <t>Ecole de sages_femmes</t>
+  </si>
+  <si>
+    <t>275</t>
+  </si>
+  <si>
+    <t>Ecole de masseurs-kinésithérapeutes</t>
+  </si>
+  <si>
+    <t>276</t>
+  </si>
+  <si>
+    <t>Ecole de laborantins d'analyses médicales</t>
+  </si>
+  <si>
+    <t>277</t>
+  </si>
+  <si>
+    <t>Ecole de péricultrices</t>
+  </si>
+  <si>
+    <t>278</t>
+  </si>
+  <si>
+    <t>Etablissement de formation polyvalent</t>
+  </si>
+  <si>
+    <t>279</t>
+  </si>
+  <si>
+    <t>Ecole de service social</t>
+  </si>
+  <si>
+    <t>280</t>
+  </si>
+  <si>
+    <t>Ecole d'éducateurs spécialisés</t>
+  </si>
+  <si>
+    <t>281</t>
+  </si>
+  <si>
+    <t>Centre de formation d'aides soignants</t>
+  </si>
+  <si>
+    <t>282</t>
+  </si>
+  <si>
+    <t>Ecole de pédicures-podologues</t>
+  </si>
+  <si>
+    <t>283</t>
+  </si>
+  <si>
+    <t>Ecole de manipulateurs d'électro-radiologie</t>
+  </si>
+  <si>
+    <t>284</t>
+  </si>
+  <si>
+    <t>Ecole de travailleuses familiales</t>
+  </si>
+  <si>
+    <t>285</t>
+  </si>
+  <si>
+    <t>Centres de Loisirs sans Hébergement</t>
+  </si>
+  <si>
+    <t>286</t>
+  </si>
+  <si>
+    <t>Service de prévention spécialisée</t>
+  </si>
+  <si>
+    <t>289</t>
+  </si>
+  <si>
+    <t>Centre de Soins Infirmiers</t>
+  </si>
+  <si>
+    <t>292</t>
+  </si>
+  <si>
+    <t>Centre Hospitalier Spécialisé lutte Maladies Mentales</t>
+  </si>
+  <si>
+    <t>294</t>
+  </si>
+  <si>
+    <t>Centre de Consultations Cancer</t>
+  </si>
+  <si>
+    <t>295</t>
+  </si>
+  <si>
+    <t>Service AEMO et AED</t>
+  </si>
+  <si>
+    <t>297</t>
+  </si>
+  <si>
+    <t>Dispensaire Polyvalent</t>
+  </si>
+  <si>
+    <t>300</t>
+  </si>
+  <si>
+    <t>Ecoles Formant aux Professions Sanitaires</t>
+  </si>
+  <si>
+    <t>303</t>
+  </si>
+  <si>
+    <t>Ecole de conseillers en économie sociale et familiale</t>
+  </si>
+  <si>
+    <t>304</t>
+  </si>
+  <si>
+    <t>Ecole d'ergothérapeutes</t>
+  </si>
+  <si>
+    <t>305</t>
+  </si>
+  <si>
+    <t>Ecole de psycho-motriciens</t>
+  </si>
+  <si>
+    <t>306</t>
+  </si>
+  <si>
+    <t>Ecole d'infirmiers anesthésistes</t>
+  </si>
+  <si>
+    <t>307</t>
+  </si>
+  <si>
+    <t>Ecole d'infirmiers de bloc opératoire</t>
+  </si>
+  <si>
+    <t>308</t>
+  </si>
+  <si>
+    <t>Centre de formation professionnelle de secteur psychiatrique</t>
+  </si>
+  <si>
+    <t>309</t>
+  </si>
+  <si>
+    <t>Ecole de cadres infirmiers</t>
+  </si>
+  <si>
+    <t>310</t>
+  </si>
+  <si>
+    <t>Ecole de cadres de secteur psychiatrique</t>
+  </si>
+  <si>
+    <t>311</t>
+  </si>
+  <si>
+    <t>Ecole de cadres de masseurs-kinésithérapeutes</t>
+  </si>
+  <si>
+    <t>312</t>
+  </si>
+  <si>
+    <t>Ecole de cadres de manipulateurs d'électro-radiologie</t>
+  </si>
+  <si>
+    <t>313</t>
+  </si>
+  <si>
+    <t>Ecole d'éducateurs de jeunes enfants</t>
+  </si>
+  <si>
+    <t>314</t>
+  </si>
+  <si>
+    <t>Ecole d'éducateurs techniques spécialisés</t>
+  </si>
+  <si>
+    <t>315</t>
+  </si>
+  <si>
+    <t>Ecole de moniteurs-éducateurs</t>
+  </si>
+  <si>
+    <t>316</t>
+  </si>
+  <si>
+    <t>Ecole d'aides médico-psychologiques</t>
+  </si>
+  <si>
+    <t>317</t>
+  </si>
+  <si>
+    <t>Ecole d'animateurs socio-éducatifs</t>
+  </si>
+  <si>
+    <t>319</t>
+  </si>
+  <si>
+    <t>Inst. régional de formation des travailleurs sociaux</t>
+  </si>
+  <si>
+    <t>320</t>
+  </si>
+  <si>
+    <t>S.A.M.U. et Centre 15</t>
+  </si>
+  <si>
     <t>321</t>
   </si>
   <si>
-    <t>Code</t>
-  </si>
-  <si>
-    <t>Uri</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>dateValid</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateValid</t>
-  </si>
-  <si>
-    <t>Date de validité d'un code concept</t>
-  </si>
-  <si>
-    <t>dateTime</t>
-  </si>
-  <si>
-    <t>dateMaj</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateMaj</t>
-  </si>
-  <si>
-    <t>Date de mise à jour d'un code concept</t>
-  </si>
-  <si>
-    <t>dateFin</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateFin</t>
-  </si>
-  <si>
-    <t>Date de fin d'exploitation d'un code concept</t>
-  </si>
-  <si>
-    <t>deprecationDate</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/concept-properties#deprecationDate</t>
-  </si>
-  <si>
-    <t>Date Concept was deprecated</t>
-  </si>
-  <si>
-    <t>status</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/concept-properties#status</t>
-  </si>
-  <si>
-    <t>A property that indicates the status of the concept.</t>
-  </si>
-  <si>
-    <t>code</t>
-  </si>
-  <si>
-    <t>retirementDate</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/concept-properties#retirementDate</t>
-  </si>
-  <si>
-    <t>Date Concept was retired</t>
-  </si>
-  <si>
-    <t>Level</t>
-  </si>
-  <si>
-    <t>Display</t>
-  </si>
-  <si>
-    <t>Definition</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>001</t>
-  </si>
-  <si>
-    <t>Autres lits de m.R.</t>
-  </si>
-  <si>
-    <t>002</t>
-  </si>
-  <si>
-    <t>Autres places de l-f.</t>
-  </si>
-  <si>
-    <t>003</t>
-  </si>
-  <si>
-    <t>Autres lits de l-s</t>
-  </si>
-  <si>
-    <t>101</t>
-  </si>
-  <si>
-    <t>Centre Hospitalier Régional (C.H.R.)</t>
-  </si>
-  <si>
-    <t>106</t>
-  </si>
-  <si>
-    <t>Centre hospitalier, ex Hôpital local</t>
-  </si>
-  <si>
-    <t>108</t>
-  </si>
-  <si>
-    <t>Etablissement de Convalescence et de Repos</t>
-  </si>
-  <si>
-    <t>109</t>
-  </si>
-  <si>
-    <t>Etablissement de santé privé autorisé en SSR</t>
-  </si>
-  <si>
-    <t>112</t>
-  </si>
-  <si>
-    <t>Centre de Convalescence Cure ou Réadaptation</t>
-  </si>
-  <si>
-    <t>114</t>
-  </si>
-  <si>
-    <t>Hôpital des armées</t>
-  </si>
-  <si>
-    <t>115</t>
-  </si>
-  <si>
-    <t>Etablissement de Soins du Service de Santé des Armées</t>
-  </si>
-  <si>
-    <t>119</t>
-  </si>
-  <si>
-    <t>Maison de Régime</t>
-  </si>
-  <si>
-    <t>122</t>
-  </si>
-  <si>
-    <t>Etablissement Soins Obstétriques Chirurgico-Gynécologiques</t>
-  </si>
-  <si>
-    <t>124</t>
-  </si>
-  <si>
-    <t>Centre de Santé</t>
-  </si>
-  <si>
-    <t>125</t>
-  </si>
-  <si>
-    <t>Centre de Santé Dentaire</t>
-  </si>
-  <si>
-    <t>126</t>
-  </si>
-  <si>
-    <t>Etablissement Thermal</t>
-  </si>
-  <si>
-    <t>127</t>
-  </si>
-  <si>
-    <t>Hospitalisation à Domicile</t>
-  </si>
-  <si>
-    <t>128</t>
-  </si>
-  <si>
-    <t>Etablissement de Soins Chirurgicaux</t>
-  </si>
-  <si>
-    <t>129</t>
-  </si>
-  <si>
-    <t>Etablissement de Soins Médicaux</t>
-  </si>
-  <si>
-    <t>130</t>
-  </si>
-  <si>
-    <t>Centre de Soins Médicaux</t>
-  </si>
-  <si>
-    <t>131</t>
-  </si>
-  <si>
-    <t>Centre de Lutte Contre Cancer</t>
-  </si>
-  <si>
-    <t>132</t>
-  </si>
-  <si>
-    <t>Etablissement de Transfusion Sanguine</t>
-  </si>
-  <si>
-    <t>135</t>
-  </si>
-  <si>
-    <t>Etablissement Réadaptation Fonctionnelle</t>
-  </si>
-  <si>
-    <t>136</t>
-  </si>
-  <si>
-    <t>Banque de Sperme</t>
-  </si>
-  <si>
-    <t>137</t>
-  </si>
-  <si>
-    <t>Banque d'Organes</t>
-  </si>
-  <si>
-    <t>138</t>
-  </si>
-  <si>
-    <t>Centre de Dialyse Périodique</t>
-  </si>
-  <si>
-    <t>139</t>
-  </si>
-  <si>
-    <t>Centre de Dialyse et d'entraînement à la Dialyse</t>
-  </si>
-  <si>
-    <t>140</t>
-  </si>
-  <si>
-    <t>Centre d'Entraînement à la Dialyse</t>
-  </si>
-  <si>
-    <t>141</t>
-  </si>
-  <si>
-    <t>Centre de dialyse</t>
-  </si>
-  <si>
-    <t>142</t>
-  </si>
-  <si>
-    <t>Dispensaire Antituberculeux</t>
-  </si>
-  <si>
-    <t>143</t>
-  </si>
-  <si>
-    <t>Centre de Vaccination BCG</t>
-  </si>
-  <si>
-    <t>144</t>
-  </si>
-  <si>
-    <t>Etablissement de Lutte Contre la Tuberculose</t>
-  </si>
-  <si>
-    <t>146</t>
-  </si>
-  <si>
-    <t>Structure d'Alternative à la dialyse en centre</t>
-  </si>
-  <si>
-    <t>156</t>
-  </si>
-  <si>
-    <t>Centre Médico-Psychologique (C.M.P.)</t>
-  </si>
-  <si>
-    <t>157</t>
-  </si>
-  <si>
-    <t>Centre de Postcure</t>
-  </si>
-  <si>
-    <t>159</t>
-  </si>
-  <si>
-    <t>Centre Parental</t>
-  </si>
-  <si>
-    <t>160</t>
-  </si>
-  <si>
-    <t>Centre de Soins Spécifiques pour Toxicomanes (C.S.S.T.)</t>
-  </si>
-  <si>
-    <t>161</t>
-  </si>
-  <si>
-    <t>Maison de Santé pour Maladies Mentales</t>
-  </si>
-  <si>
-    <t>162</t>
-  </si>
-  <si>
-    <t>Centre de Cure Ambulatoire en Alcoologie (C.C.A.A.)</t>
-  </si>
-  <si>
-    <t>163</t>
-  </si>
-  <si>
-    <t>Maison d'Enfants à Caractère Sanitaire Temporaire</t>
-  </si>
-  <si>
-    <t>164</t>
-  </si>
-  <si>
-    <t>Etablissements Expérimentaux Accueil de la Petite Enfance</t>
-  </si>
-  <si>
-    <t>165</t>
-  </si>
-  <si>
-    <t>Appartement de Coordination Thérapeutique (A.C.T.)</t>
-  </si>
-  <si>
-    <t>166</t>
-  </si>
-  <si>
-    <t>Centre Parents-Enfants de moins de 3 ans</t>
-  </si>
-  <si>
-    <t>167</t>
-  </si>
-  <si>
-    <t>Crèche Collective</t>
-  </si>
-  <si>
-    <t>168</t>
-  </si>
-  <si>
-    <t>Service Accueil Familial pour la Petite Enfance</t>
-  </si>
-  <si>
-    <t>169</t>
-  </si>
-  <si>
-    <t>Crèche Multi Accueil Collectif et Familial</t>
-  </si>
-  <si>
-    <t>170</t>
-  </si>
-  <si>
-    <t>Halte Garderie</t>
-  </si>
-  <si>
-    <t>171</t>
-  </si>
-  <si>
-    <t>Garderie et Jardin d'Enfants</t>
-  </si>
-  <si>
-    <t>172</t>
-  </si>
-  <si>
-    <t>Pouponnière à Caractère Social</t>
-  </si>
-  <si>
-    <t>173</t>
-  </si>
-  <si>
-    <t>Pouponnière à Caractère Sanitaire</t>
-  </si>
-  <si>
-    <t>174</t>
-  </si>
-  <si>
-    <t>Etablissement d'Accueil Collectif Régulier et Occasionnel</t>
-  </si>
-  <si>
-    <t>175</t>
-  </si>
-  <si>
-    <t>Foyer de l'Enfance</t>
-  </si>
-  <si>
-    <t>176</t>
-  </si>
-  <si>
-    <t>Village d'Enfants</t>
-  </si>
-  <si>
-    <t>177</t>
-  </si>
-  <si>
-    <t>Maison d'Enfants à Caractère Social</t>
-  </si>
-  <si>
-    <t>178</t>
-  </si>
-  <si>
-    <t>Ctre.Accueil- Accomp.Réduc.Risq.Usag. Drogues (C.A.A.R.U.D.)</t>
-  </si>
-  <si>
-    <t>179</t>
-  </si>
-  <si>
-    <t>Maison d'Enfants à Caractère Sanitaire Permanente</t>
-  </si>
-  <si>
-    <t>180</t>
-  </si>
-  <si>
-    <t>Lits Halte Soins Santé (L.H.S.S.)</t>
-  </si>
-  <si>
-    <t>181</t>
-  </si>
-  <si>
-    <t>Maison Familiale de Vacances</t>
-  </si>
-  <si>
-    <t>182</t>
-  </si>
-  <si>
-    <t>Service d'Éducation Spéciale et de Soins à Domicile</t>
-  </si>
-  <si>
-    <t>183</t>
-  </si>
-  <si>
-    <t>Institut Médico-Educatif (I.M.E.)</t>
-  </si>
-  <si>
-    <t>184</t>
-  </si>
-  <si>
-    <t>Institut Médico-Pédagogique (I.M.P.)</t>
-  </si>
-  <si>
-    <t>185</t>
-  </si>
-  <si>
-    <t>Institut Médico-Professionnel (I.M.Pro.)</t>
-  </si>
-  <si>
-    <t>186</t>
-  </si>
-  <si>
-    <t>Institut Thérapeutique Éducatif et Pédagogique (I.T.E.P.)</t>
-  </si>
-  <si>
-    <t>188</t>
-  </si>
-  <si>
-    <t>Etablissement pour Enfants ou Adolescents Polyhandicapés</t>
-  </si>
-  <si>
-    <t>189</t>
-  </si>
-  <si>
-    <t>Centre Médico-Psycho-Pédagogique (C.M.P.P.)</t>
-  </si>
-  <si>
-    <t>190</t>
-  </si>
-  <si>
-    <t>Centre Action Médico-Sociale Précoce (C.A.M.S.P.)</t>
-  </si>
-  <si>
-    <t>191</t>
-  </si>
-  <si>
-    <t>Etablissement pour Déficients Moteurs Cérébraux</t>
-  </si>
-  <si>
-    <t>192</t>
-  </si>
-  <si>
-    <t>Institut d'éducation motrice</t>
-  </si>
-  <si>
-    <t>193</t>
-  </si>
-  <si>
-    <t>Etablissement pour Déficients Moteurs et Moteurs Cérébraux</t>
-  </si>
-  <si>
-    <t>194</t>
-  </si>
-  <si>
-    <t>Institut pour Déficients Visuels</t>
-  </si>
-  <si>
-    <t>195</t>
-  </si>
-  <si>
-    <t>Institut pour Déficients Auditifs</t>
-  </si>
-  <si>
-    <t>196</t>
-  </si>
-  <si>
-    <t>Institut d'Education Sensorielle Sourd-Aveugle</t>
-  </si>
-  <si>
-    <t>197</t>
-  </si>
-  <si>
-    <t>Centre soins accompagnement prévention addictologie (CSAPA)</t>
-  </si>
-  <si>
-    <t>198</t>
-  </si>
-  <si>
-    <t>Établissement et Service de Préorientation</t>
-  </si>
-  <si>
-    <t>199</t>
-  </si>
-  <si>
-    <t>Hospice</t>
-  </si>
-  <si>
-    <t>200</t>
-  </si>
-  <si>
-    <t>Maison de Retraite</t>
-  </si>
-  <si>
-    <t>202</t>
-  </si>
-  <si>
-    <t>Résidences autonomie</t>
-  </si>
-  <si>
-    <t>205</t>
-  </si>
-  <si>
-    <t>Foyer Club Restaurant</t>
-  </si>
-  <si>
-    <t>207</t>
-  </si>
-  <si>
-    <t>Centre de Jour pour Personnes Agées</t>
-  </si>
-  <si>
-    <t>208</t>
-  </si>
-  <si>
-    <t>Service d'Aide Ménagère à Domicile</t>
-  </si>
-  <si>
-    <t>209</t>
-  </si>
-  <si>
-    <t>Service autonomie aide et soins (SAAS)</t>
-  </si>
-  <si>
-    <t>212</t>
-  </si>
-  <si>
-    <t>Alarme Médico-Sociale</t>
-  </si>
-  <si>
-    <t>213</t>
-  </si>
-  <si>
-    <t>Lits d'Accueil Médicalisés (L.A.M.)</t>
-  </si>
-  <si>
-    <t>214</t>
-  </si>
-  <si>
-    <t>Centre Hébergement &amp; Réinsertion Sociale (C.H.R.S.)</t>
-  </si>
-  <si>
-    <t>215</t>
-  </si>
-  <si>
-    <t>Maison Relai</t>
-  </si>
-  <si>
-    <t>216</t>
-  </si>
-  <si>
-    <t>Résidence Hôtelière à Vocation Sociale (R.H.V.S)</t>
-  </si>
-  <si>
-    <t>217</t>
-  </si>
-  <si>
-    <t>Cité de Transit</t>
-  </si>
-  <si>
-    <t>218</t>
-  </si>
-  <si>
-    <t>Aire Station Nomades</t>
-  </si>
-  <si>
-    <t>219</t>
-  </si>
-  <si>
-    <t>Autre Centre d'Accueil</t>
-  </si>
-  <si>
-    <t>220</t>
-  </si>
-  <si>
-    <t>Centre Social</t>
-  </si>
-  <si>
-    <t>221</t>
-  </si>
-  <si>
-    <t>Bureau d'Aide Psychologique Universitaire (B.A.P.U.)</t>
-  </si>
-  <si>
-    <t>223</t>
-  </si>
-  <si>
-    <t>Protection Maternelle et Infantile (P.M.I.)</t>
-  </si>
-  <si>
-    <t>224</t>
-  </si>
-  <si>
-    <t>Etablissement de Consultation Pré et Post-natale</t>
-  </si>
-  <si>
-    <t>225</t>
-  </si>
-  <si>
-    <t>Consultations de Nourrissons</t>
-  </si>
-  <si>
-    <t>228</t>
-  </si>
-  <si>
-    <t>Centre de Santé Sexuelle</t>
-  </si>
-  <si>
-    <t>229</t>
-  </si>
-  <si>
-    <t>Consultation Problèmes naissance</t>
-  </si>
-  <si>
-    <t>230</t>
-  </si>
-  <si>
-    <t>Etablissement Consultation Protection Infantile</t>
-  </si>
-  <si>
-    <t>231</t>
-  </si>
-  <si>
-    <t>Espaces de vie affective, relationnelle et sexuelle (EVARS)</t>
-  </si>
-  <si>
-    <t>233</t>
-  </si>
-  <si>
-    <t>Lactarium</t>
-  </si>
-  <si>
-    <t>236</t>
-  </si>
-  <si>
-    <t>Centre Placement Familial Socio-Educatif (C.P.F.S.E.)</t>
-  </si>
-  <si>
-    <t>237</t>
-  </si>
-  <si>
-    <t>Centre de Placement Familial Spécialisé</t>
-  </si>
-  <si>
-    <t>238</t>
-  </si>
-  <si>
-    <t>Centre d'Accueil Familial Spécialisé</t>
-  </si>
-  <si>
-    <t>241</t>
-  </si>
-  <si>
-    <t>Établissement de Placement</t>
-  </si>
-  <si>
-    <t>242</t>
-  </si>
-  <si>
-    <t>Service d’Activité de Jour</t>
-  </si>
-  <si>
-    <t>246</t>
-  </si>
-  <si>
-    <t>Etablissement et Service d'Aide par le Travail (E.S.A.T.)</t>
-  </si>
-  <si>
-    <t>247</t>
-  </si>
-  <si>
-    <t>Entreprise adaptée</t>
-  </si>
-  <si>
-    <t>249</t>
-  </si>
-  <si>
-    <t>Établissement et Service de Réadaptation Professionnelle</t>
-  </si>
-  <si>
-    <t>250</t>
-  </si>
-  <si>
-    <t>Centre Réentrainement au travail</t>
-  </si>
-  <si>
-    <t>251</t>
-  </si>
-  <si>
-    <t>Maison Vacances pour Handicapés</t>
-  </si>
-  <si>
-    <t>252</t>
-  </si>
-  <si>
-    <t>Foyer Hébergement Adultes Handicapés</t>
-  </si>
-  <si>
-    <t>253</t>
-  </si>
-  <si>
-    <t>Foyer d'Accueil Polyvalent pour Adultes Handicapés</t>
-  </si>
-  <si>
-    <t>255</t>
-  </si>
-  <si>
-    <t>Maison d'Accueil Spécialisée (M.A.S.)</t>
-  </si>
-  <si>
-    <t>256</t>
-  </si>
-  <si>
-    <t>Foyer Travailleurs Migrants non transformé en Résidence Soc.</t>
-  </si>
-  <si>
-    <t>257</t>
-  </si>
-  <si>
-    <t>Foyers de jeunes travailleurs</t>
-  </si>
-  <si>
-    <t>258</t>
-  </si>
-  <si>
-    <t>Maisons Relais - Pensions de Famille</t>
-  </si>
-  <si>
-    <t>259</t>
-  </si>
-  <si>
-    <t>Autres résidences sociales</t>
-  </si>
-  <si>
-    <t>261</t>
-  </si>
-  <si>
-    <t>D.D.A.S.S.</t>
-  </si>
-  <si>
-    <t>262</t>
-  </si>
-  <si>
-    <t>Etablissement Régional d'Enseignement Adapté</t>
-  </si>
-  <si>
-    <t>265</t>
-  </si>
-  <si>
-    <t>Section Education Spéciale Classe Atelier</t>
-  </si>
-  <si>
-    <t>266</t>
-  </si>
-  <si>
-    <t>Dispensaire Antivénérien</t>
-  </si>
-  <si>
-    <t>267</t>
-  </si>
-  <si>
-    <t>Dispensaire Antihansénien</t>
-  </si>
-  <si>
-    <t>268</t>
-  </si>
-  <si>
-    <t>Centre Médico-Scolaire</t>
-  </si>
-  <si>
-    <t>269</t>
-  </si>
-  <si>
-    <t>Centre de Médecine Universitaire</t>
-  </si>
-  <si>
-    <t>270</t>
-  </si>
-  <si>
-    <t>Centre de Médecine Sportive</t>
-  </si>
-  <si>
-    <t>271</t>
-  </si>
-  <si>
-    <t>Maison d'accueil Hospitalière</t>
-  </si>
-  <si>
-    <t>272</t>
-  </si>
-  <si>
-    <t>Ecole d'ambulanciers</t>
-  </si>
-  <si>
-    <t>273</t>
-  </si>
-  <si>
-    <t>Institut de formation en soins infirmiers (I.F.S.I.)</t>
-  </si>
-  <si>
-    <t>274</t>
-  </si>
-  <si>
-    <t>Ecole de sages_femmes</t>
-  </si>
-  <si>
-    <t>275</t>
-  </si>
-  <si>
-    <t>Ecole de masseurs-kinésithérapeutes</t>
-  </si>
-  <si>
-    <t>276</t>
-  </si>
-  <si>
-    <t>Ecole de laborantins d'analyses médicales</t>
-  </si>
-  <si>
-    <t>277</t>
-  </si>
-  <si>
-    <t>Ecole de péricultrices</t>
-  </si>
-  <si>
-    <t>278</t>
-  </si>
-  <si>
-    <t>Etablissement de formation polyvalent</t>
-  </si>
-  <si>
-    <t>279</t>
-  </si>
-  <si>
-    <t>Ecole de service social</t>
-  </si>
-  <si>
-    <t>280</t>
-  </si>
-  <si>
-    <t>Ecole d'éducateurs spécialisés</t>
-  </si>
-  <si>
-    <t>281</t>
-  </si>
-  <si>
-    <t>Centre de formation d'aides soignants</t>
-  </si>
-  <si>
-    <t>282</t>
-  </si>
-  <si>
-    <t>Ecole de pédicures-podologues</t>
-  </si>
-  <si>
-    <t>283</t>
-  </si>
-  <si>
-    <t>Ecole de manipulateurs d'électro-radiologie</t>
-  </si>
-  <si>
-    <t>284</t>
-  </si>
-  <si>
-    <t>Ecole de travailleuses familiales</t>
-  </si>
-  <si>
-    <t>285</t>
-  </si>
-  <si>
-    <t>Centres de Loisirs sans Hébergement</t>
-  </si>
-  <si>
-    <t>286</t>
-  </si>
-  <si>
-    <t>Service de prévention spécialisée</t>
-  </si>
-  <si>
-    <t>289</t>
-  </si>
-  <si>
-    <t>Centre de Soins Infirmiers</t>
-  </si>
-  <si>
-    <t>292</t>
-  </si>
-  <si>
-    <t>Centre Hospitalier Spécialisé lutte Maladies Mentales</t>
-  </si>
-  <si>
-    <t>294</t>
-  </si>
-  <si>
-    <t>Centre de Consultations Cancer</t>
-  </si>
-  <si>
-    <t>295</t>
-  </si>
-  <si>
-    <t>Service AEMO et AED</t>
-  </si>
-  <si>
-    <t>297</t>
-  </si>
-  <si>
-    <t>Dispensaire Polyvalent</t>
-  </si>
-  <si>
-    <t>300</t>
-  </si>
-  <si>
-    <t>Ecoles Formant aux Professions Sanitaires</t>
-  </si>
-  <si>
-    <t>303</t>
-  </si>
-  <si>
-    <t>Ecole de conseillers en économie sociale et familiale</t>
-  </si>
-  <si>
-    <t>304</t>
-  </si>
-  <si>
-    <t>Ecole d'ergothérapeutes</t>
-  </si>
-  <si>
-    <t>305</t>
-  </si>
-  <si>
-    <t>Ecole de psycho-motriciens</t>
-  </si>
-  <si>
-    <t>306</t>
-  </si>
-  <si>
-    <t>Ecole d'infirmiers anesthésistes</t>
-  </si>
-  <si>
-    <t>307</t>
-  </si>
-  <si>
-    <t>Ecole d'infirmiers de bloc opératoire</t>
-  </si>
-  <si>
-    <t>308</t>
-  </si>
-  <si>
-    <t>Centre de formation professionnelle de secteur psychiatrique</t>
-  </si>
-  <si>
-    <t>309</t>
-  </si>
-  <si>
-    <t>Ecole de cadres infirmiers</t>
-  </si>
-  <si>
-    <t>310</t>
-  </si>
-  <si>
-    <t>Ecole de cadres de secteur psychiatrique</t>
-  </si>
-  <si>
-    <t>311</t>
-  </si>
-  <si>
-    <t>Ecole de cadres de masseurs-kinésithérapeutes</t>
-  </si>
-  <si>
-    <t>312</t>
-  </si>
-  <si>
-    <t>Ecole de cadres de manipulateurs d'électro-radiologie</t>
-  </si>
-  <si>
-    <t>313</t>
-  </si>
-  <si>
-    <t>Ecole d'éducateurs de jeunes enfants</t>
-  </si>
-  <si>
-    <t>314</t>
-  </si>
-  <si>
-    <t>Ecole d'éducateurs techniques spécialisés</t>
-  </si>
-  <si>
-    <t>315</t>
-  </si>
-  <si>
-    <t>Ecole de moniteurs-éducateurs</t>
-  </si>
-  <si>
-    <t>316</t>
-  </si>
-  <si>
-    <t>Ecole d'aides médico-psychologiques</t>
-  </si>
-  <si>
-    <t>317</t>
-  </si>
-  <si>
-    <t>Ecole d'animateurs socio-éducatifs</t>
-  </si>
-  <si>
-    <t>319</t>
-  </si>
-  <si>
-    <t>Inst. régional de formation des travailleurs sociaux</t>
-  </si>
-  <si>
-    <t>320</t>
-  </si>
-  <si>
-    <t>S.A.M.U. et Centre 15</t>
-  </si>
-  <si>
     <t>Unité Mobile Hospitalière</t>
   </si>
   <si>
-    <t>322</t>
-  </si>
-  <si>
     <t>Centre Rég.Informatiq.Hospit.</t>
   </si>
   <si>
@@ -2141,6 +2141,12 @@
   </si>
   <si>
     <t>Points locaux d'information dédiés aux personnes âgées. Ces services peuvent être rattachés à des CCAS ( Centre Communaux d'Action Sociale)</t>
+  </si>
+  <si>
+    <t>705</t>
+  </si>
+  <si>
+    <t>Groupe d’Entraide Mutuelle (GEM)</t>
   </si>
 </sst>
 </file>
@@ -2556,7 +2562,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D322"/>
+  <dimension ref="A1:D323"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -4522,10 +4528,10 @@
         <v>61</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>34</v>
+        <v>386</v>
       </c>
       <c r="C164" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D164" s="2"/>
     </row>
@@ -4534,7 +4540,7 @@
         <v>61</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>387</v>
+        <v>34</v>
       </c>
       <c r="C165" t="s" s="2">
         <v>388</v>
@@ -6439,6 +6445,20 @@
       </c>
       <c r="D322" t="s" s="2">
         <v>708</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="B323" t="s" s="2">
+        <v>709</v>
+      </c>
+      <c r="C323" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="D323" t="s" s="2">
+        <v>699</v>
       </c>
     </row>
   </sheetData>
